--- a/outputs/daily/hr_rankings_2026-09-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-22.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>50</v>
       </c>
       <c r="U2" t="n">
-        <v>60.1</v>
+        <v>64.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -873,22 +873,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Hot streak: 5 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1287,27 +1287,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>691181</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Emmanuel Rodriguez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22T22:40:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1317,26 +1317,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Anthony Molina</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>683627</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>53.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,26 +1350,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>58.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.2</v>
+        <v>49.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>45</v>
+        <v>25.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1435,124 +1435,124 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 13/24 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.4714</t>
+          <t>102.985</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.492</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.473</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-22T22:35:00Z</t>
+          <t>2026-09-22T22:40:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1598,21 +1598,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,26 +1626,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>52.8</v>
+        <v>58.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>47.5</v>
+        <v>32.2</v>
       </c>
       <c r="R5" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S5" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>42.3</v>
+        <v>45</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1701,134 +1701,134 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Contact streak: 13/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.5295</t>
+          <t>101.4714</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2195</t>
+          <t>0.239</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3227</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.47</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2207</t>
+          <t>0.267</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4291</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -1839,27 +1839,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691181</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Emmanuel Rodriguez</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:35:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Anthony Molina</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>683627</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.4</v>
+        <v>52.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,26 +1902,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>70.90000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.6</v>
+        <v>47.5</v>
       </c>
       <c r="R6" t="n">
-        <v>19.3</v>
+        <v>32.1</v>
       </c>
       <c r="S6" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>40.7</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1977,27 +1977,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,104 +2007,104 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>102.985</t>
+          <t>102.5295</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2195</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3227</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.47</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>49.48</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.2207</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.4291</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2391,27 +2391,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>683002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-22T22:40:00Z</t>
+          <t>2026-09-22T22:35:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -2454,26 +2454,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.2</v>
+        <v>47.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S8" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>42.3</v>
+        <v>65.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2529,134 +2529,134 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>90.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.5427</t>
+          <t>101.2113</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.5036</t>
+          <t>0.4047</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2459</t>
+          <t>0.1504</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.53</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>45.56</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2098</t>
+          <t>0.171</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.4291</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2667,27 +2667,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:40:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2697,26 +2697,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Anthony Molina</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>683627</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,26 +2730,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>51.4</v>
+        <v>62</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.6</v>
+        <v>32.2</v>
       </c>
       <c r="R9" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8</v>
+        <v>42.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2805,37 +2805,37 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -2845,94 +2845,94 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.71</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.3868</t>
+          <t>102.5427</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4566</t>
+          <t>0.5036</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2076</t>
+          <t>0.2459</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3324</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2231</t>
+          <t>0.2098</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2943,27 +2943,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>683002</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-22T22:35:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2973,17 +2973,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Anthony Molina</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>683627</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,26 +3006,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>51.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>47.5</v>
+        <v>49.6</v>
       </c>
       <c r="R10" t="n">
-        <v>32.1</v>
+        <v>19.3</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>61.5</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,27 +3081,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,104 +3111,104 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>91.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.2113</t>
+          <t>101.3868</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4047</t>
+          <t>0.4566</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1504</t>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3324</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>0.2231</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4291</t>
+          <t>0.473</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>78.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>681297</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-09-22T22:35:00Z</t>
@@ -5181,17 +5181,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5214,26 +5214,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>53.1</v>
+        <v>43.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>30.8</v>
+        <v>47.5</v>
       </c>
       <c r="R18" t="n">
         <v>32.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>34.9</v>
+        <v>32</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5289,127 +5289,127 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>101.2775</t>
+          <t>100.825</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.4026</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.3077</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.4291</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1364</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -5427,24 +5427,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>681297</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-09-22T22:35:00Z</t>
@@ -5457,17 +5457,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,26 +5490,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>43.2</v>
+        <v>53.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>47.5</v>
+        <v>30.8</v>
       </c>
       <c r="R19" t="n">
         <v>32.1</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5565,127 +5565,127 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.825</t>
+          <t>101.2775</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4026</t>
+          <t>0.448</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4291</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1364</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>33.7</v>
+        <v>30.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/9, 1 HR</t>
+          <t>Last 7 games: 2/10, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -6255,27 +6255,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22T22:40:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Anthony Molina</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>683627</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6318,26 +6318,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>40.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="R22" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S22" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U22" t="n">
-        <v>36.3</v>
+        <v>60.3</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -6408,119 +6408,119 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 14.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>101.0317</t>
+          <t>97.727</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4119</t>
+          <t>0.3579</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.2813</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>73.83</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.473</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6531,27 +6531,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22T22:40:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6561,26 +6561,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>43.7</v>
+        <v>44.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6594,26 +6594,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>42.3</v>
+        <v>20.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>32.2</v>
+        <v>48</v>
       </c>
       <c r="R23" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S23" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>16.6</v>
+        <v>68.7</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6669,27 +6669,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6699,104 +6699,104 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>100.5196</t>
+          <t>98.2572</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>0.3787</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1955</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.3134</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.1544</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.54</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6807,27 +6807,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:40:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Anthony Molina</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>683627</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6874,13 +6874,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>39.1</v>
+        <v>40.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.6</v>
+        <v>36</v>
       </c>
       <c r="R24" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S24" t="n">
         <v>81.90000000000001</v>
@@ -6889,7 +6889,7 @@
         <v>50</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>36.3</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -6945,134 +6945,134 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>100.8312</t>
+          <t>101.0317</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4119</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3412</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>73.83</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1877</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:40:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7113,26 +7113,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Anthony Molina</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>683627</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>43.3</v>
+        <v>43.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7146,26 +7146,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>21.4</v>
+        <v>42.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>49</v>
+        <v>32.2</v>
       </c>
       <c r="R25" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S25" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T25" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U25" t="n">
-        <v>39.7</v>
+        <v>16.6</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -7236,119 +7236,119 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Contact streak: 10/26 over last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>97.727</t>
+          <t>100.5196</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.3579</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1955</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.2813</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7359,24 +7359,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>691785</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marcelo Mayer</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>2026-09-23T01:45:00Z</t>
@@ -7389,17 +7389,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Anthony Molina</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>683627</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>43.3</v>
+        <v>43.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7422,26 +7422,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>25.1</v>
+        <v>39.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>49.6</v>
       </c>
       <c r="R26" t="n">
         <v>19.3</v>
       </c>
       <c r="S26" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
@@ -7512,112 +7512,112 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 1/23, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>99.0278</t>
+          <t>100.8312</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.2602</t>
+          <t>0.3412</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>74.42</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>37.24</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1166</t>
+          <t>0.1877</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.473</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr"/>
@@ -7635,27 +7635,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>543807</t>
+          <t>691785</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Marcelo Mayer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22T22:35:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7698,26 +7698,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>39.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>30.8</v>
+        <v>48</v>
       </c>
       <c r="R27" t="n">
-        <v>32.1</v>
+        <v>19.3</v>
       </c>
       <c r="S27" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>16.1</v>
+        <v>14.6</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7803,104 +7803,104 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.3154</t>
+          <t>99.0278</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4331</t>
+          <t>0.3123</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.2602</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>73.31</t>
+          <t>74.42</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1866</t>
+          <t>0.1166</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>43.54</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1364</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -7911,12 +7911,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>672386</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>42.3</v>
+        <v>43.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>29.2</v>
+        <v>39.3</v>
       </c>
       <c r="Q28" t="n">
         <v>30.8</v>
@@ -7987,13 +7987,13 @@
         <v>32.1</v>
       </c>
       <c r="S28" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T28" t="n">
         <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>52.3</v>
+        <v>16.1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8049,22 +8049,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -8079,67 +8079,67 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>89.07</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>100.4738</t>
+          <t>100.3154</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4058</t>
+          <t>0.4331</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1365</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>71.94</t>
+          <t>73.31</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1866</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -8187,27 +8187,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>672386</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:35:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8217,17 +8217,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8236,7 +8236,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>41.8</v>
+        <v>42.3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8250,26 +8250,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>20.6</v>
+        <v>29.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>30.8</v>
       </c>
       <c r="R29" t="n">
-        <v>19.3</v>
+        <v>32.1</v>
       </c>
       <c r="S29" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T29" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U29" t="n">
-        <v>18.3</v>
+        <v>52.3</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8325,27 +8325,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/10, 1 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8355,104 +8355,104 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>98.2572</t>
+          <t>100.4738</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3787</t>
+          <t>0.4058</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>71.94</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>21.41</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1544</t>
+          <t>0.1411</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1364</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8545,7 +8545,7 @@
         <v>80</v>
       </c>
       <c r="U30" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8601,12 +8601,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 11/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -8821,7 +8821,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>38.8</v>
+        <v>38.4</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>40.9</v>
+        <v>32</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -10957,7 +10957,7 @@
         <v>50</v>
       </c>
       <c r="U39" t="n">
-        <v>46.8</v>
+        <v>48.7</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>695391</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Brett Harris</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -11214,11 +11214,11 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>10.1</v>
+        <v>14.5</v>
       </c>
       <c r="Q40" t="n">
         <v>48</v>
@@ -11227,13 +11227,13 @@
         <v>19.3</v>
       </c>
       <c r="S40" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U40" t="n">
-        <v>20.3</v>
+        <v>17.7</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -11289,27 +11289,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 1 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -11319,67 +11319,67 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.29</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>97.9832</t>
+          <t>97.8527</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.252</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.0787</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.2602</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.0722</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -11427,12 +11427,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>695391</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brett Harris</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11490,11 +11490,11 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>14.5</v>
+        <v>10.1</v>
       </c>
       <c r="Q41" t="n">
         <v>48</v>
@@ -11503,13 +11503,13 @@
         <v>19.3</v>
       </c>
       <c r="S41" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T41" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U41" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -11565,27 +11565,27 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 1/13, 1 HR</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -11595,67 +11595,67 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>97.8527</t>
+          <t>97.9832</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.0787</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.2602</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0722</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>35.3</v>
+        <v>35.9</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>50</v>
       </c>
       <c r="U42" t="n">
-        <v>5.1</v>
+        <v>16.6</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 0 HR</t>
+          <t>Last 7 games: 1/18, 0 HR</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>80</v>
       </c>
       <c r="U53" t="n">
-        <v>10.1</v>
+        <v>0.8</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>50</v>
       </c>
       <c r="U54" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15081,12 +15081,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>50</v>
       </c>
       <c r="U2" t="n">
-        <v>60.1</v>
+        <v>64.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -15959,22 +15959,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Hot streak: 5 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -16373,27 +16373,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>691181</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Emmanuel Rodriguez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22T22:40:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -16403,26 +16403,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Anthony Molina</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>683627</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>53.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -16436,26 +16436,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>58.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.2</v>
+        <v>49.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>45</v>
+        <v>25.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -16521,124 +16521,124 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 13/24 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.4714</t>
+          <t>102.985</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.492</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.473</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -16649,27 +16649,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-22T22:35:00Z</t>
+          <t>2026-09-22T22:40:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -16684,21 +16684,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -16712,26 +16712,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>52.8</v>
+        <v>58.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>47.5</v>
+        <v>32.2</v>
       </c>
       <c r="R5" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S5" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>42.3</v>
+        <v>45</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -16787,134 +16787,134 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Contact streak: 13/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.5295</t>
+          <t>101.4714</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2195</t>
+          <t>0.239</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3227</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.47</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2207</t>
+          <t>0.267</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4291</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -16925,27 +16925,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691181</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Emmanuel Rodriguez</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:35:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16955,17 +16955,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Anthony Molina</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>683627</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.4</v>
+        <v>52.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -16988,26 +16988,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>70.90000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.6</v>
+        <v>47.5</v>
       </c>
       <c r="R6" t="n">
-        <v>19.3</v>
+        <v>32.1</v>
       </c>
       <c r="S6" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>40.7</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -17063,27 +17063,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -17093,104 +17093,104 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>102.985</t>
+          <t>102.5295</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2195</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3227</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.47</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>49.48</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.2207</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.4291</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -17477,27 +17477,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>683002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-22T22:40:00Z</t>
+          <t>2026-09-22T22:35:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -17540,26 +17540,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.2</v>
+        <v>47.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S8" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>42.3</v>
+        <v>65.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -17615,134 +17615,134 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>90.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.5427</t>
+          <t>101.2113</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.5036</t>
+          <t>0.4047</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2459</t>
+          <t>0.1504</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.53</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>45.56</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2098</t>
+          <t>0.171</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.4291</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -17753,27 +17753,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23T01:45:00Z</t>
+          <t>2026-09-22T22:40:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -17783,26 +17783,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Anthony Molina</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>683627</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -17816,26 +17816,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>51.4</v>
+        <v>62</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.6</v>
+        <v>32.2</v>
       </c>
       <c r="R9" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8</v>
+        <v>42.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -17891,37 +17891,37 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -17931,94 +17931,94 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.71</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.3868</t>
+          <t>102.5427</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4566</t>
+          <t>0.5036</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2076</t>
+          <t>0.2459</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3324</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2231</t>
+          <t>0.2098</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>683002</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-22T22:35:00Z</t>
+          <t>2026-09-23T01:45:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -18059,17 +18059,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Anthony Molina</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>683627</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -18092,26 +18092,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>51.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>47.5</v>
+        <v>49.6</v>
       </c>
       <c r="R10" t="n">
-        <v>32.1</v>
+        <v>19.3</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>61.5</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -18167,27 +18167,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 5.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -18197,104 +18197,104 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>91.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.2113</t>
+          <t>101.3868</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4047</t>
+          <t>0.4566</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1504</t>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3324</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>0.2231</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4291</t>
+          <t>0.473</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -19734,7 +19734,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>78.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -20237,24 +20237,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>681297</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-09-22T22:35:00Z</t>
@@ -20267,17 +20267,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -20300,26 +20300,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>53.1</v>
+        <v>43.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>30.8</v>
+        <v>47.5</v>
       </c>
       <c r="R18" t="n">
         <v>32.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>34.9</v>
+        <v>32</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -20375,127 +20375,127 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>101.2775</t>
+          <t>100.825</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.4026</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.3077</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.4291</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1364</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -20513,24 +20513,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>681297</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-09-22T22:35:00Z</t>
@@ -20543,17 +20543,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -20562,7 +20562,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -20576,26 +20576,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>43.2</v>
+        <v>53.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>47.5</v>
+        <v>30.8</v>
       </c>
       <c r="R19" t="n">
         <v>32.1</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -20651,127 +20651,127 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.825</t>
+          <t>101.2775</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4026</t>
+          <t>0.448</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4291</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1364</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>33.7</v>
+        <v>30.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/9, 1 HR</t>
+          <t>Last 7 games: 2/10, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
